--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>127028714</v>
       </c>
       <c r="B18" t="n">
-        <v>98265</v>
+        <v>98340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127028712</v>
       </c>
       <c r="B19" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028698</v>
+        <v>127028740</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>80115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460401</v>
+        <v>460327</v>
       </c>
       <c r="R20" t="n">
-        <v>6990348</v>
+        <v>6990471</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127028740</v>
+        <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>80084</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460327</v>
+        <v>460401</v>
       </c>
       <c r="R21" t="n">
-        <v>6990471</v>
+        <v>6990348</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2698,7 +2698,7 @@
         <v>127028724</v>
       </c>
       <c r="B22" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127028699</v>
       </c>
       <c r="B23" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>127028730</v>
       </c>
       <c r="B24" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>127028718</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127028707</v>
       </c>
       <c r="B26" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127028732</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>127028714</v>
       </c>
       <c r="B18" t="n">
-        <v>98340</v>
+        <v>98346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127028712</v>
       </c>
       <c r="B19" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>127028740</v>
       </c>
       <c r="B20" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127028724</v>
       </c>
       <c r="B22" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127028699</v>
       </c>
       <c r="B23" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>127028730</v>
       </c>
       <c r="B24" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>127028718</v>
       </c>
       <c r="B25" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127028707</v>
       </c>
       <c r="B26" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127028732</v>
       </c>
       <c r="B27" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>127028714</v>
       </c>
       <c r="B18" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127028712</v>
       </c>
       <c r="B19" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127028699</v>
       </c>
       <c r="B23" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127028732</v>
       </c>
       <c r="B27" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028740</v>
+        <v>127028698</v>
       </c>
       <c r="B20" t="n">
-        <v>80118</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460327</v>
+        <v>460401</v>
       </c>
       <c r="R20" t="n">
-        <v>6990471</v>
+        <v>6990348</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127028698</v>
+        <v>127028740</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>80118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460401</v>
+        <v>460327</v>
       </c>
       <c r="R21" t="n">
-        <v>6990348</v>
+        <v>6990471</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028698</v>
+        <v>127028740</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>80118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460401</v>
+        <v>460327</v>
       </c>
       <c r="R20" t="n">
-        <v>6990348</v>
+        <v>6990471</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127028740</v>
+        <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>80118</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460327</v>
+        <v>460401</v>
       </c>
       <c r="R21" t="n">
-        <v>6990471</v>
+        <v>6990348</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>127028714</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127028712</v>
       </c>
       <c r="B19" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>127028740</v>
       </c>
       <c r="B20" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127028724</v>
       </c>
       <c r="B22" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127028699</v>
       </c>
       <c r="B23" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>127028730</v>
       </c>
       <c r="B24" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>127028718</v>
       </c>
       <c r="B25" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127028707</v>
       </c>
       <c r="B26" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127028732</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028740</v>
+        <v>127028698</v>
       </c>
       <c r="B20" t="n">
-        <v>80122</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460327</v>
+        <v>460401</v>
       </c>
       <c r="R20" t="n">
-        <v>6990471</v>
+        <v>6990348</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127028698</v>
+        <v>127028740</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>80122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460401</v>
+        <v>460327</v>
       </c>
       <c r="R21" t="n">
-        <v>6990348</v>
+        <v>6990471</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028698</v>
+        <v>127028740</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>80122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460401</v>
+        <v>460327</v>
       </c>
       <c r="R20" t="n">
-        <v>6990348</v>
+        <v>6990471</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127028740</v>
+        <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>80122</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460327</v>
+        <v>460401</v>
       </c>
       <c r="R21" t="n">
-        <v>6990471</v>
+        <v>6990348</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>127028714</v>
       </c>
       <c r="B18" t="n">
-        <v>98351</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127028699</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127028732</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>127028714</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>98354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127028712</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028740</v>
+        <v>127028698</v>
       </c>
       <c r="B20" t="n">
-        <v>80122</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460327</v>
+        <v>460401</v>
       </c>
       <c r="R20" t="n">
-        <v>6990471</v>
+        <v>6990348</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127028698</v>
+        <v>127028740</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>80124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460401</v>
+        <v>460327</v>
       </c>
       <c r="R21" t="n">
-        <v>6990348</v>
+        <v>6990471</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2698,7 +2698,7 @@
         <v>127028724</v>
       </c>
       <c r="B22" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127028699</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>127028730</v>
       </c>
       <c r="B24" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>127028718</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127028707</v>
       </c>
       <c r="B26" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127028732</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028698</v>
+        <v>127028740</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>80124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460401</v>
+        <v>460327</v>
       </c>
       <c r="R20" t="n">
-        <v>6990348</v>
+        <v>6990471</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127028740</v>
+        <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>80124</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460327</v>
+        <v>460401</v>
       </c>
       <c r="R21" t="n">
-        <v>6990471</v>
+        <v>6990348</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>127028714</v>
       </c>
       <c r="B18" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127028712</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127028699</v>
       </c>
       <c r="B23" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127028732</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>127028714</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>98340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127028712</v>
       </c>
       <c r="B19" t="n">
-        <v>91356</v>
+        <v>91337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>127028740</v>
       </c>
       <c r="B20" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>127028698</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127028724</v>
       </c>
       <c r="B22" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127028699</v>
       </c>
       <c r="B23" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>127028730</v>
       </c>
       <c r="B24" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>127028718</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127028707</v>
       </c>
       <c r="B26" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127028732</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114578356</v>
+        <v>114577548</v>
       </c>
       <c r="B2" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460360</v>
+        <v>460389</v>
       </c>
       <c r="R2" t="n">
-        <v>6990482</v>
+        <v>6990501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,53 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114578354</v>
+        <v>127028707</v>
       </c>
       <c r="B3" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460353</v>
+        <v>460386</v>
       </c>
       <c r="R3" t="n">
-        <v>6990484</v>
+        <v>6990363</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114576977</v>
+        <v>127028724</v>
       </c>
       <c r="B4" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460289</v>
+        <v>460357</v>
       </c>
       <c r="R4" t="n">
-        <v>6990439</v>
+        <v>6990350</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,65 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114576992</v>
+        <v>127028730</v>
       </c>
       <c r="B5" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460385</v>
+        <v>460349</v>
       </c>
       <c r="R5" t="n">
-        <v>6990535</v>
+        <v>6990268</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114577592</v>
+        <v>127028740</v>
       </c>
       <c r="B6" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460386</v>
+        <v>460327</v>
       </c>
       <c r="R6" t="n">
-        <v>6990506</v>
+        <v>6990471</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,49 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114576988</v>
+        <v>114575494</v>
       </c>
       <c r="B7" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460383</v>
+        <v>460328</v>
       </c>
       <c r="R7" t="n">
-        <v>6990486</v>
+        <v>6990339</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114577548</v>
+        <v>114575497</v>
       </c>
       <c r="B8" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460389</v>
+        <v>460286</v>
       </c>
       <c r="R8" t="n">
-        <v>6990501</v>
+        <v>6990471</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114576986</v>
+        <v>114575498</v>
       </c>
       <c r="B9" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460333</v>
+        <v>460300</v>
       </c>
       <c r="R9" t="n">
-        <v>6990479</v>
+        <v>6990468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114578352</v>
+        <v>114575500</v>
       </c>
       <c r="B10" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460331</v>
+        <v>460314</v>
       </c>
       <c r="R10" t="n">
-        <v>6990479</v>
+        <v>6990495</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114577589</v>
+        <v>114575501</v>
       </c>
       <c r="B11" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460372</v>
+        <v>460329</v>
       </c>
       <c r="R11" t="n">
-        <v>6990293</v>
+        <v>6990486</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,53 +1645,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114577497</v>
+        <v>127028752</v>
       </c>
       <c r="B12" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460373</v>
+        <v>460300</v>
       </c>
       <c r="R12" t="n">
-        <v>6990483</v>
+        <v>6990295</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,49 +1730,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114578353</v>
+        <v>114577589</v>
       </c>
       <c r="B13" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460335</v>
+        <v>460372</v>
       </c>
       <c r="R13" t="n">
-        <v>6990480</v>
+        <v>6990293</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114576987</v>
+        <v>114577591</v>
       </c>
       <c r="B14" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460349</v>
+        <v>460271</v>
       </c>
       <c r="R14" t="n">
-        <v>6990491</v>
+        <v>6990394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114577094</v>
+        <v>114577592</v>
       </c>
       <c r="B15" t="n">
-        <v>97554</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460372</v>
+        <v>460386</v>
       </c>
       <c r="R15" t="n">
-        <v>6990480</v>
+        <v>6990506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,53 +2033,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114578355</v>
+        <v>127028694</v>
       </c>
       <c r="B16" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460358</v>
+        <v>460416</v>
       </c>
       <c r="R16" t="n">
-        <v>6990481</v>
+        <v>6990507</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2173,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,65 +2118,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114578357</v>
+        <v>127028701</v>
       </c>
       <c r="B17" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460366</v>
+        <v>460397</v>
       </c>
       <c r="R17" t="n">
-        <v>6990480</v>
+        <v>6990376</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2275,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2295,44 +2215,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127028714</v>
+        <v>127028703</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2342,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460384</v>
+        <v>460394</v>
       </c>
       <c r="R18" t="n">
-        <v>6990376</v>
+        <v>6990459</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2404,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127028712</v>
+        <v>127028718</v>
       </c>
       <c r="B19" t="n">
-        <v>91356</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460385</v>
+        <v>460376</v>
       </c>
       <c r="R19" t="n">
-        <v>6990345</v>
+        <v>6990294</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2501,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028740</v>
+        <v>127028709</v>
       </c>
       <c r="B20" t="n">
-        <v>80124</v>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460327</v>
+        <v>460385</v>
       </c>
       <c r="R20" t="n">
-        <v>6990471</v>
+        <v>6990284</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,48 +2518,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127028698</v>
+        <v>114576977</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>99035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460401</v>
+        <v>460289</v>
       </c>
       <c r="R21" t="n">
-        <v>6990348</v>
+        <v>6990439</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2663,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2683,60 +2603,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127028724</v>
+        <v>114576981</v>
       </c>
       <c r="B22" t="n">
-        <v>80124</v>
+        <v>99035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460357</v>
+        <v>460295</v>
       </c>
       <c r="R22" t="n">
-        <v>6990350</v>
+        <v>6990473</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2760,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,22 +2700,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127028699</v>
+        <v>114576982</v>
       </c>
       <c r="B23" t="n">
-        <v>98477</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,37 +2723,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460399</v>
+        <v>460301</v>
       </c>
       <c r="R23" t="n">
-        <v>6990353</v>
+        <v>6990466</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2857,12 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,60 +2797,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127028730</v>
+        <v>114576984</v>
       </c>
       <c r="B24" t="n">
-        <v>80124</v>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460349</v>
+        <v>460325</v>
       </c>
       <c r="R24" t="n">
-        <v>6990268</v>
+        <v>6990506</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2954,12 +2874,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2974,60 +2894,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127028718</v>
+        <v>114576985</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>99035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460376</v>
+        <v>460324</v>
       </c>
       <c r="R25" t="n">
-        <v>6990294</v>
+        <v>6990487</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3051,12 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3071,60 +2991,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127028707</v>
+        <v>114576986</v>
       </c>
       <c r="B26" t="n">
-        <v>80124</v>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460386</v>
+        <v>460333</v>
       </c>
       <c r="R26" t="n">
-        <v>6990363</v>
+        <v>6990479</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3148,12 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3168,60 +3088,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127028732</v>
+        <v>114576987</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460347</v>
+        <v>460349</v>
       </c>
       <c r="R27" t="n">
-        <v>6990310</v>
+        <v>6990491</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3245,12 +3165,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3265,15 +3185,2246 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114576988</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>460383</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6990486</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>114576992</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>460385</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6990535</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114578351</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>460296</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6990470</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>114578352</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>460331</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6990479</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>114578353</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>460335</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6990480</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>114578354</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>460353</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6990484</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>114578355</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>460358</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6990481</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114578356</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>460360</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6990482</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114578357</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>460366</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6990480</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127028744</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>460316</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6990486</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Klas Andersson</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Klas Andersson</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114577094</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>460372</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6990480</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127028714</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>460384</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6990376</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127028698</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>460401</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6990348</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127028713</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>460385</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6990405</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127028727</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>460354</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6990266</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127028732</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>460347</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6990310</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>114577497</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>460373</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6990483</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>114577499</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>460407</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6990526</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>114578393</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>460270</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6990450</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>114578394</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>460331</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6990507</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>114578398</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>460372</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6990548</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127028689</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>460420</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6990348</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127028699</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>460399</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6990353</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45111-2022 artfynd.xlsx
+++ b/artfynd/A 45111-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577548</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028707</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028724</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028730</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028740</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575494</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575497</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575498</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575500</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575501</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028752</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577589</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577591</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577592</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028694</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028701</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028703</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028718</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028709</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114576977</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114576981</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114576982</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114576984</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114576985</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114576986</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114576987</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114576988</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114576992</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578351</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578352</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578353</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578354</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578355</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578356</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578357</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028744</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577094</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028714</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028698</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028713</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028727</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028732</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577497</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577499</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578393</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578394</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578398</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028689</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,8 +5670,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028699</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>